--- a/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
+++ b/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
@@ -2505,7 +2505,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="D553" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9D13" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5586,7 +5586,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9067" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DFB2" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -8793,7 +8793,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9643" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F095" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:O4"/>
   </mergeCells>
@@ -11869,7 +11869,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AA59" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EA60" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -11988,7 +11988,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="A515" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B275" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -18143,7 +18143,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DF5B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D7F8" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -22354,7 +22354,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F7A3" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C4D9" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:P4"/>
   </mergeCells>
@@ -28526,7 +28526,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="ED24" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8403" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -28650,7 +28650,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="90C3" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="835F" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -32436,7 +32436,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="CF19" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E1BB" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -36526,7 +36526,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="996A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C78A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -40682,7 +40682,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F3FA" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D8A3" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -46878,7 +46878,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EF34" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C3E4" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>
@@ -52249,7 +52249,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EAFE" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A565" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:AD4"/>
   </mergeCells>
@@ -56469,7 +56469,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A4F0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DEAA" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
+++ b/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
@@ -52,7 +52,7 @@
     <t>version_dwc_sc_rnaseq</t>
   </si>
   <si>
-    <t>Single-cell Ribonucleic Acid Sequencing Sequencing [Darwin Core]</t>
+    <t>Single-cell Ribonucleic Acid Sequencing [Darwin Core]</t>
   </si>
   <si>
     <t>For single-cell Ribonucleic Acid Sequencing (RNA-seq)  studies aimed focused on biodiversity-related information in alignment with the Darwin Core (DwC) standard.</t>
@@ -2457,7 +2457,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="146.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -2505,7 +2505,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="D553" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B153" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5586,7 +5586,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9067" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A892" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -8793,7 +8793,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9643" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E2BE" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:O4"/>
   </mergeCells>
@@ -11869,7 +11869,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AA59" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C66B" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -11988,7 +11988,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="A515" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8AA9" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -18143,7 +18143,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DF5B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A082" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -22354,7 +22354,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F7A3" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="AE76" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:P4"/>
   </mergeCells>
@@ -28526,7 +28526,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="ED24" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F708" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -28650,7 +28650,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="90C3" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D6FC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -32436,7 +32436,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="CF19" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DBF1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -36526,7 +36526,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="996A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A034" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -40682,7 +40682,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F3FA" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A666" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -46878,7 +46878,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EF34" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BFFB" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>
@@ -52249,7 +52249,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EAFE" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FF1A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:AD4"/>
   </mergeCells>
@@ -56469,7 +56469,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A4F0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DCB0" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
+++ b/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="680">
   <si>
     <t>key</t>
   </si>
@@ -835,6 +835,12 @@
     <t>Cdna</t>
   </si>
   <si>
+    <t>Cdna Oligo Dt</t>
+  </si>
+  <si>
+    <t>Cdna Randompriming</t>
+  </si>
+  <si>
     <t>Chip</t>
   </si>
   <si>
@@ -850,6 +856,9 @@
     <t>Hybrid Selection</t>
   </si>
   <si>
+    <t>Inverse Rrna</t>
+  </si>
+  <si>
     <t>Inverse Rrna Selection</t>
   </si>
   <si>
@@ -880,6 +889,9 @@
     <t>Pcr</t>
   </si>
   <si>
+    <t>Polya</t>
+  </si>
+  <si>
     <t>Race</t>
   </si>
   <si>
@@ -968,6 +980,9 @@
   </si>
   <si>
     <t>Ncrna-Seq</t>
+  </si>
+  <si>
+    <t>Nome-Seq</t>
   </si>
   <si>
     <t>Poolclone</t>
@@ -2505,7 +2520,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="B153" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FED8" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2527,16 +2542,16 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2544,16 +2559,16 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2561,16 +2576,16 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5586,7 +5601,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A892" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="971B" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -5634,46 +5649,46 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -5681,46 +5696,46 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -5728,46 +5743,46 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -8793,7 +8808,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="E2BE" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DB6D" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:O4"/>
   </mergeCells>
@@ -8820,13 +8835,13 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8834,13 +8849,13 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8848,13 +8863,13 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -11869,7 +11884,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C66B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="CD45" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -11899,80 +11914,80 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="5" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -11988,7 +12003,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="8AA9" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FF9A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -12021,34 +12036,34 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>165</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -12056,34 +12071,34 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>193</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -12097,28 +12112,28 @@
         <v>194</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -18143,7 +18158,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A082" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F7C1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -18184,49 +18199,49 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -18234,49 +18249,49 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -18284,37 +18299,37 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>258</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>258</v>
@@ -22354,7 +22369,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AE76" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="AF3D" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:P4"/>
   </mergeCells>
@@ -22404,34 +22419,34 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>165</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -22439,34 +22454,34 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -22474,31 +22489,31 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>194</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>29</v>
@@ -28526,7 +28541,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F708" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BBD1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -28650,7 +28665,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="D6FC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="82C8" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -28684,12 +28699,12 @@
   <sheetData>
     <row r="5" spans="4:30">
       <c r="D5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="4:30">
       <c r="D6" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -28698,12 +28713,12 @@
         <v>265</v>
       </c>
       <c r="AD6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="4:30">
       <c r="D7" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
@@ -28712,12 +28727,12 @@
         <v>266</v>
       </c>
       <c r="AD7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="4:30">
       <c r="D8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F8" t="s">
         <v>41</v>
@@ -28726,12 +28741,12 @@
         <v>267</v>
       </c>
       <c r="AD8" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="4:30">
       <c r="D9" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
@@ -28740,12 +28755,12 @@
         <v>268</v>
       </c>
       <c r="AD9" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="4:30">
       <c r="D10" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F10" t="s">
         <v>43</v>
@@ -28754,12 +28769,12 @@
         <v>269</v>
       </c>
       <c r="AD10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="4:30">
       <c r="D11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
@@ -28768,12 +28783,12 @@
         <v>270</v>
       </c>
       <c r="AD11" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="4:30">
       <c r="D12" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F12" t="s">
         <v>45</v>
@@ -28782,12 +28797,12 @@
         <v>271</v>
       </c>
       <c r="AD12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="4:30">
       <c r="D13" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F13" t="s">
         <v>46</v>
@@ -28796,530 +28811,545 @@
         <v>272</v>
       </c>
       <c r="AD13" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="4:30">
       <c r="D14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AB14" t="s">
         <v>273</v>
       </c>
       <c r="AD14" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="4:30">
       <c r="D15" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AB15" t="s">
         <v>274</v>
       </c>
       <c r="AD15" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="4:30">
       <c r="D16" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AB16" t="s">
         <v>275</v>
       </c>
       <c r="AD16" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="4:30">
       <c r="D17" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AB17" t="s">
         <v>276</v>
       </c>
       <c r="AD17" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="4:30">
       <c r="D18" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AB18" t="s">
         <v>277</v>
       </c>
       <c r="AD18" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="4:30">
       <c r="D19" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AB19" t="s">
         <v>278</v>
       </c>
       <c r="AD19" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="4:30">
       <c r="D20" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AB20" t="s">
         <v>279</v>
       </c>
       <c r="AD20" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="4:30">
       <c r="D21" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AB21" t="s">
         <v>280</v>
       </c>
       <c r="AD21" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="4:30">
       <c r="D22" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AB22" t="s">
         <v>281</v>
       </c>
       <c r="AD22" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="4:30">
       <c r="D23" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AB23" t="s">
         <v>282</v>
       </c>
       <c r="AD23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="4:30">
       <c r="D24" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AB24" t="s">
         <v>283</v>
       </c>
       <c r="AD24" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="4:30">
       <c r="D25" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AB25" t="s">
         <v>284</v>
       </c>
       <c r="AD25" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="4:30">
       <c r="D26" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AB26" t="s">
         <v>285</v>
       </c>
       <c r="AD26" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="4:30">
       <c r="D27" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AB27" t="s">
         <v>286</v>
       </c>
       <c r="AD27" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="4:30">
       <c r="D28" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AB28" t="s">
         <v>287</v>
       </c>
       <c r="AD28" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="4:30">
       <c r="D29" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AB29" t="s">
         <v>288</v>
       </c>
       <c r="AD29" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="4:30">
       <c r="D30" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AB30" t="s">
         <v>289</v>
       </c>
       <c r="AD30" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="4:30">
       <c r="D31" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AB31" t="s">
         <v>290</v>
       </c>
       <c r="AD31" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="4:30">
       <c r="D32" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AB32" t="s">
         <v>291</v>
       </c>
       <c r="AD32" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="4:30">
       <c r="D33" t="s">
-        <v>401</v>
+        <v>406</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>292</v>
       </c>
       <c r="AD33" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" spans="4:30">
       <c r="D34" t="s">
-        <v>402</v>
+        <v>407</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>293</v>
       </c>
       <c r="AD34" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="4:30">
       <c r="D35" t="s">
-        <v>403</v>
+        <v>408</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>294</v>
       </c>
       <c r="AD35" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="4:30">
       <c r="D36" t="s">
-        <v>404</v>
+        <v>409</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>295</v>
       </c>
       <c r="AD36" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="4:30">
       <c r="D37" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AD37" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38" spans="4:30">
       <c r="D38" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AD38" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="4:30">
       <c r="D39" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AD39" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="4:30">
       <c r="D40" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AD40" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" spans="4:30">
       <c r="D41" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AD41" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="4:30">
       <c r="D42" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AD42" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="4:30">
       <c r="D43" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AD43" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="44" spans="4:30">
       <c r="D44" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AD44" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="4:30">
       <c r="D45" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AD45" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="4:30">
       <c r="D46" t="s">
-        <v>414</v>
+        <v>419</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="4:30">
       <c r="D47" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="48" spans="4:30">
       <c r="D48" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="52" spans="4:4">
       <c r="D52" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="85" spans="4:4">
       <c r="D85" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="86" spans="4:4">
       <c r="D86" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -32436,7 +32466,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8C47" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -36526,7 +36556,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A034" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D8D6" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -40682,7 +40712,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A666" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="92BB" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -46878,7 +46908,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="BFFB" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E1A5" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>
@@ -52249,7 +52279,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="FF1A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C639" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:AD4"/>
   </mergeCells>
@@ -52281,13 +52311,13 @@
       <formula1>",Cd41+,Cd41-"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AB5:AB1005">
-      <formula1>HiddenDropdowns!$AB$5:$AB$32</formula1>
+      <formula1>HiddenDropdowns!$AB$5:$AB$36</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AC5:AC1005">
-      <formula1>",Genomic,Metagenomic,Metatranscriptomic,Other,Synthetic,Transcriptomic,Viral Rna"</formula1>
+      <formula1>",Genomic,Genomic Single Cell,Metagenomic,Metatranscriptomic,Other,Synthetic,Transcriptomic,Transcriptomic Single Cell,Viral Rna"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AD5:AD1005">
-      <formula1>HiddenDropdowns!$AD$5:$AD$45</formula1>
+      <formula1>HiddenDropdowns!$AD$5:$AD$46</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52319,43 +52349,43 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -52363,43 +52393,43 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -52407,43 +52437,43 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>150</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>150</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -56469,7 +56499,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DCB0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B4C7" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
+++ b/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
@@ -2520,7 +2520,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="FED8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A6E8" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5601,7 +5601,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="971B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EEF2" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -8808,7 +8808,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DB6D" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F6BF" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:O4"/>
   </mergeCells>
@@ -11884,7 +11884,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="CD45" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C343" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -12003,7 +12003,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="FF9A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DC34" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -18158,7 +18158,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F7C1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9DB6" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -22369,7 +22369,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AF3D" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F7B0" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:P4"/>
   </mergeCells>
@@ -28541,7 +28541,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="BBD1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A066" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -28665,7 +28665,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="82C8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9F1C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -32466,7 +32466,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8C47" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8F2B" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -36556,7 +36556,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D8D6" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="901C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -40712,7 +40712,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="92BB" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A20C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -46908,7 +46908,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="E1A5" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="815C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>
@@ -52279,7 +52279,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C639" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F775" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:AD4"/>
   </mergeCells>
@@ -56499,7 +56499,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="B4C7" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="AEAD" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
+++ b/dist/checklists/xlsx/dwc/single_cell_manifest_version_dwc_sc_rnaseq_v0.4.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="702">
   <si>
     <t>key</t>
   </si>
@@ -418,16 +418,13 @@
     <t>Cell Size</t>
   </si>
   <si>
-    <t>Suspension Volume (µL)</t>
-  </si>
-  <si>
     <t>Suspension Concentration Cells Per µL</t>
   </si>
   <si>
     <t>Suspension Dilution</t>
   </si>
   <si>
-    <t>Loading Volume Μl</t>
+    <t>Loading Volume of Cell Suspension (µL)</t>
   </si>
   <si>
     <t>Suspension Dilution Buffer</t>
@@ -484,15 +481,6 @@
     <t>e.g. 10</t>
   </si>
   <si>
-    <t>Suspension Volume (µL) (optional)</t>
-  </si>
-  <si>
-    <t>The volume of the cell suspension in microlitres (µL).</t>
-  </si>
-  <si>
-    <t>e.g. 100</t>
-  </si>
-  <si>
     <t>Suspension Concentration Cells Per µL (optional)</t>
   </si>
   <si>
@@ -511,10 +499,10 @@
     <t>e.g. 1:10</t>
   </si>
   <si>
-    <t>Loading Volume Μl (optional)</t>
-  </si>
-  <si>
-    <t>The volume of the cell suspension loaded into the single-cell RNA-sequencing system for analysis.</t>
+    <t>Loading Volume of Cell Suspension (µL) (optional)</t>
+  </si>
+  <si>
+    <t>The volume of the cell suspension loaded into the single-cell RNA-sequencing system for analysis in microlitres (µL).</t>
   </si>
   <si>
     <t>Suspension Dilution Buffer (optional)</t>
@@ -580,12 +568,6 @@
     <t>Dual or Single Index</t>
   </si>
   <si>
-    <t>I5 Sequence</t>
-  </si>
-  <si>
-    <t>i7 Sequence</t>
-  </si>
-  <si>
     <t>Plate ID</t>
   </si>
   <si>
@@ -733,13 +715,13 @@
     <t>e.g. 1:1000</t>
   </si>
   <si>
-    <t>Barcode sequence used on the i5 adapter during library preparation for identifying samples in multiplexed single-cell RNA-sequencing.</t>
+    <t>Barcode sequence used on the i5 adapter during library preparation for identifying samples in multiplexed single-cell RNA-sequencing. The DNA barcode sequence (A, C, G, T), not a plate or well identifier should be specified.</t>
   </si>
   <si>
     <t>e.g. ATCACG</t>
   </si>
   <si>
-    <t>Barcode sequence used on the i7 adapter to distinguish samples in multiplexed sequencing runs.</t>
+    <t>Barcode sequence used on the i7 adapter to distinguish samples in multiplexed sequencing runs. The nucleotide sequence (A, C, G, T), not a plate or well identifier should be specified.</t>
   </si>
   <si>
     <t>e.g. CGATGT</t>
@@ -751,18 +733,6 @@
     <t>e.g. Dual</t>
   </si>
   <si>
-    <t>The nucleotide sequence of the i5 index used in multiplexing during sequencing.</t>
-  </si>
-  <si>
-    <t>e.g. ATCGTAGC</t>
-  </si>
-  <si>
-    <t>The specific nucleotide sequence of the i7 index used for a sample.</t>
-  </si>
-  <si>
-    <t>e.g. TGCATGCA</t>
-  </si>
-  <si>
     <t>Plate ID (optional)</t>
   </si>
   <si>
@@ -1424,6 +1394,30 @@
   </si>
   <si>
     <t>Other Derived Cell Attributes</t>
+  </si>
+  <si>
+    <t>Number of Cells Analysed</t>
+  </si>
+  <si>
+    <t>Genes Detected per Cell</t>
+  </si>
+  <si>
+    <t>Cell-level QC Threshold</t>
+  </si>
+  <si>
+    <t>Number of Clusters or Cell Populations</t>
+  </si>
+  <si>
+    <t>Main Single-cell Response</t>
+  </si>
+  <si>
+    <t>Separation Score</t>
+  </si>
+  <si>
+    <t>Number of Candidate Genes</t>
+  </si>
+  <si>
+    <t>Key Analysis Method or Threshold</t>
   </si>
   <si>
     <t>File Derived From (optional)</t>
@@ -1461,6 +1455,78 @@
   </si>
   <si>
     <t>e.g. Cluster</t>
+  </si>
+  <si>
+    <t>Number of Cells Analysed (optional)</t>
+  </si>
+  <si>
+    <t>Total number of cells retained after quality-control filtering and included in the downstream analysis.</t>
+  </si>
+  <si>
+    <t>e.g. 12458</t>
+  </si>
+  <si>
+    <t>Genes Detected per Cell (optional)</t>
+  </si>
+  <si>
+    <t>Mean or median number of genes detected per cell among the cells included in the analysis.</t>
+  </si>
+  <si>
+    <t>e.g. 1842</t>
+  </si>
+  <si>
+    <t>Cell-level QC Threshold (optional)</t>
+  </si>
+  <si>
+    <t>Criteria and cut-off values used to retain or exclude individual cells from downstream analysis.</t>
+  </si>
+  <si>
+    <t>e.g. ≥200 genes, ≤5,000 genes, &lt;15% mitochondrial reads</t>
+  </si>
+  <si>
+    <t>Number of Clusters or Cell Populations (optional)</t>
+  </si>
+  <si>
+    <t>Total number of computationally identified clusters or annotated cell populations reported in the study.</t>
+  </si>
+  <si>
+    <t>e.g. 8</t>
+  </si>
+  <si>
+    <t>Main Single-cell Response (optional)</t>
+  </si>
+  <si>
+    <t>Principal biological response or finding identified through the single-cell analysis.</t>
+  </si>
+  <si>
+    <t>e.g. Increased interferon signalling in macrophages</t>
+  </si>
+  <si>
+    <t>Separation Score (optional)</t>
+  </si>
+  <si>
+    <t>Reported metric used to quantify separation between experimental conditions, clusters or cell populations.</t>
+  </si>
+  <si>
+    <t>e.g. 0.62</t>
+  </si>
+  <si>
+    <t>Number of Candidate Genes (optional)</t>
+  </si>
+  <si>
+    <t>Total number of marker, switch or other candidate genes identified in the analysis.</t>
+  </si>
+  <si>
+    <t>e.g. 27</t>
+  </si>
+  <si>
+    <t>Key Analysis Method or Threshold (optional)</t>
+  </si>
+  <si>
+    <t>Principal computational method or threshold used to derive the reported downstream-analysis results.</t>
+  </si>
+  <si>
+    <t>e.g. Leiden clustering, resolution = 0.8; DE threshold: FDR &lt;0.05</t>
   </si>
   <si>
     <t>Reference Genome</t>
@@ -2520,14 +2586,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="A6E8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DB9C" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1005"/>
+  <dimension ref="A1:M1005"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -2535,60 +2601,140 @@
     <col min="3" max="3" width="112.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="185.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="65" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="90.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="82.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="84.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="92.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="73" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="96" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="91.85546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>472</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>473</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>474</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
@@ -2596,41 +2742,49 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="7"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:13">
       <c r="A6" s="7"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:13">
       <c r="A7" s="7"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:13">
       <c r="A8" s="7"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:13">
       <c r="A9" s="7"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:13">
       <c r="A10" s="7"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:13">
       <c r="A11" s="7"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:13">
       <c r="A12" s="7"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:13">
       <c r="A13" s="7"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:13">
       <c r="A14" s="7"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:13">
       <c r="A15" s="7"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:13">
       <c r="A16" s="7"/>
     </row>
     <row r="17" spans="1:1">
@@ -5601,11 +5755,11 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EEF2" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C8E3" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:E4">
+  <conditionalFormatting sqref="A1:M4">
     <cfRule type="notContainsErrors" dxfId="0" priority="1">
       <formula>NOT(ISERROR(A1))</formula>
     </cfRule>
@@ -5649,46 +5803,46 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -5696,46 +5850,46 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>525</v>
+        <v>547</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -5743,46 +5897,46 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>526</v>
+        <v>548</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -8808,7 +8962,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F6BF" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="98F0" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:O4"/>
   </mergeCells>
@@ -8835,13 +8989,13 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8849,13 +9003,13 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8863,13 +9017,13 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -11884,7 +12038,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C343" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="CD7E" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -11914,80 +12068,80 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>559</v>
+        <v>581</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>568</v>
+        <v>590</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>571</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="5" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>561</v>
+        <v>583</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -12003,7 +12157,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="DC34" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DDD3" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -12036,34 +12190,34 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>591</v>
+        <v>613</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>596</v>
+        <v>618</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -12071,34 +12225,34 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>589</v>
+        <v>611</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>594</v>
+        <v>616</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>597</v>
+        <v>619</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>600</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -12109,31 +12263,31 @@
         <v>21</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>587</v>
+        <v>609</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>595</v>
+        <v>617</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>601</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -18158,7 +18312,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9DB6" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E184" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -18199,49 +18353,49 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>631</v>
+        <v>653</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>637</v>
+        <v>659</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>642</v>
+        <v>664</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>647</v>
+        <v>669</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>649</v>
+        <v>671</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>651</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -18249,49 +18403,49 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>632</v>
+        <v>654</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>638</v>
+        <v>660</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>640</v>
+        <v>662</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>650</v>
+        <v>672</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>652</v>
+        <v>674</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -18299,49 +18453,49 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>619</v>
+        <v>641</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>624</v>
+        <v>646</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>627</v>
+        <v>649</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>641</v>
+        <v>663</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -22369,7 +22523,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F7B0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E295" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:P4"/>
   </mergeCells>
@@ -22419,34 +22573,34 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>654</v>
+        <v>676</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>655</v>
+        <v>677</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>672</v>
+        <v>694</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>675</v>
+        <v>697</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>678</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -22454,34 +22608,34 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>660</v>
+        <v>682</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>662</v>
+        <v>684</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>663</v>
+        <v>685</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>667</v>
+        <v>689</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>670</v>
+        <v>692</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>673</v>
+        <v>695</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>679</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -22489,31 +22643,31 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>661</v>
+        <v>683</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>664</v>
+        <v>686</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>666</v>
+        <v>688</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>668</v>
+        <v>690</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>671</v>
+        <v>693</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>677</v>
+        <v>699</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>29</v>
@@ -28541,7 +28695,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A066" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EB38" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -28665,7 +28819,7 @@
       <c r="H4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="9F1C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D166" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -28688,668 +28842,668 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="D5:AD87"/>
+  <dimension ref="D5:AB87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="4:30">
+    <row r="5" spans="4:28">
       <c r="D5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="4:30">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="4:28">
       <c r="D6" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
+      <c r="Z6" t="s">
+        <v>255</v>
+      </c>
       <c r="AB6" t="s">
-        <v>265</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="4:30">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="4:28">
       <c r="D7" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
       </c>
+      <c r="Z7" t="s">
+        <v>256</v>
+      </c>
       <c r="AB7" t="s">
-        <v>266</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="8" spans="4:30">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="4:28">
       <c r="D8" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="F8" t="s">
         <v>41</v>
       </c>
+      <c r="Z8" t="s">
+        <v>257</v>
+      </c>
       <c r="AB8" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="9" spans="4:30">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="4:28">
       <c r="D9" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
       </c>
+      <c r="Z9" t="s">
+        <v>258</v>
+      </c>
       <c r="AB9" t="s">
-        <v>268</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="10" spans="4:30">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="4:28">
       <c r="D10" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="F10" t="s">
         <v>43</v>
       </c>
+      <c r="Z10" t="s">
+        <v>259</v>
+      </c>
       <c r="AB10" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="11" spans="4:30">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="4:28">
       <c r="D11" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
       </c>
+      <c r="Z11" t="s">
+        <v>260</v>
+      </c>
       <c r="AB11" t="s">
-        <v>270</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="12" spans="4:30">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="4:28">
       <c r="D12" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="F12" t="s">
         <v>45</v>
       </c>
+      <c r="Z12" t="s">
+        <v>261</v>
+      </c>
       <c r="AB12" t="s">
-        <v>271</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" spans="4:30">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="4:28">
       <c r="D13" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="F13" t="s">
         <v>46</v>
       </c>
+      <c r="Z13" t="s">
+        <v>262</v>
+      </c>
       <c r="AB13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="4:28">
+      <c r="D14" t="s">
+        <v>377</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="4:28">
+      <c r="D15" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="4:28">
+      <c r="D16" t="s">
+        <v>379</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="4:28">
+      <c r="D17" t="s">
+        <v>380</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="18" spans="4:28">
+      <c r="D18" t="s">
+        <v>381</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="4:28">
+      <c r="D19" t="s">
+        <v>382</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20" spans="4:28">
+      <c r="D20" t="s">
+        <v>383</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="21" spans="4:28">
+      <c r="D21" t="s">
+        <v>384</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="4:28">
+      <c r="D22" t="s">
+        <v>385</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="4:28">
+      <c r="D23" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z23" t="s">
         <v>272</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AB23" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="14" spans="4:30">
-      <c r="D14" t="s">
+    <row r="24" spans="4:28">
+      <c r="D24" t="s">
         <v>387</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="Z24" t="s">
         <v>273</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AB24" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="15" spans="4:30">
-      <c r="D15" t="s">
+    <row r="25" spans="4:28">
+      <c r="D25" t="s">
         <v>388</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="Z25" t="s">
         <v>274</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AB25" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="4:30">
-      <c r="D16" t="s">
+    <row r="26" spans="4:28">
+      <c r="D26" t="s">
         <v>389</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="Z26" t="s">
         <v>275</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AB26" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="17" spans="4:30">
-      <c r="D17" t="s">
+    <row r="27" spans="4:28">
+      <c r="D27" t="s">
         <v>390</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="Z27" t="s">
         <v>276</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AB27" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="4:30">
-      <c r="D18" t="s">
+    <row r="28" spans="4:28">
+      <c r="D28" t="s">
         <v>391</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="Z28" t="s">
         <v>277</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AB28" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="19" spans="4:30">
-      <c r="D19" t="s">
+    <row r="29" spans="4:28">
+      <c r="D29" t="s">
         <v>392</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="Z29" t="s">
         <v>278</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AB29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="4:28">
+      <c r="D30" t="s">
+        <v>393</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB30" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="20" spans="4:30">
-      <c r="D20" t="s">
-        <v>393</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>279</v>
-      </c>
-      <c r="AD20" t="s">
+    <row r="31" spans="4:28">
+      <c r="D31" t="s">
+        <v>394</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB31" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="21" spans="4:30">
-      <c r="D21" t="s">
-        <v>394</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>280</v>
-      </c>
-      <c r="AD21" t="s">
+    <row r="32" spans="4:28">
+      <c r="D32" t="s">
+        <v>395</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>281</v>
+      </c>
+      <c r="AB32" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="22" spans="4:30">
-      <c r="D22" t="s">
-        <v>395</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>281</v>
-      </c>
-      <c r="AD22" t="s">
+    <row r="33" spans="4:28">
+      <c r="D33" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB33" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="4:30">
-      <c r="D23" t="s">
-        <v>396</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD23" t="s">
+    <row r="34" spans="4:28">
+      <c r="D34" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB34" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="24" spans="4:30">
-      <c r="D24" t="s">
-        <v>397</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>283</v>
-      </c>
-      <c r="AD24" t="s">
+    <row r="35" spans="4:28">
+      <c r="D35" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB35" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="4:30">
-      <c r="D25" t="s">
-        <v>398</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>284</v>
-      </c>
-      <c r="AD25" t="s">
+    <row r="36" spans="4:28">
+      <c r="D36" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB36" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="26" spans="4:30">
-      <c r="D26" t="s">
-        <v>399</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD26" t="s">
+    <row r="37" spans="4:28">
+      <c r="D37" t="s">
+        <v>400</v>
+      </c>
+      <c r="AB37" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="4:30">
-      <c r="D27" t="s">
-        <v>400</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>286</v>
-      </c>
-      <c r="AD27" t="s">
+    <row r="38" spans="4:28">
+      <c r="D38" t="s">
+        <v>401</v>
+      </c>
+      <c r="AB38" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="28" spans="4:30">
-      <c r="D28" t="s">
-        <v>401</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>287</v>
-      </c>
-      <c r="AD28" t="s">
+    <row r="39" spans="4:28">
+      <c r="D39" t="s">
+        <v>402</v>
+      </c>
+      <c r="AB39" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="4:30">
-      <c r="D29" t="s">
-        <v>402</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>288</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="30" spans="4:30">
-      <c r="D30" t="s">
+    <row r="40" spans="4:28">
+      <c r="D40" t="s">
         <v>403</v>
       </c>
-      <c r="AB30" t="s">
-        <v>289</v>
-      </c>
-      <c r="AD30" t="s">
+      <c r="AB40" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="31" spans="4:30">
-      <c r="D31" t="s">
+    <row r="41" spans="4:28">
+      <c r="D41" t="s">
         <v>404</v>
       </c>
-      <c r="AB31" t="s">
-        <v>290</v>
-      </c>
-      <c r="AD31" t="s">
+      <c r="AB41" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="4:30">
-      <c r="D32" t="s">
+    <row r="42" spans="4:28">
+      <c r="D42" t="s">
         <v>405</v>
       </c>
-      <c r="AB32" t="s">
-        <v>291</v>
-      </c>
-      <c r="AD32" t="s">
+      <c r="AB42" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="33" spans="4:30">
-      <c r="D33" t="s">
+    <row r="43" spans="4:28">
+      <c r="D43" t="s">
         <v>406</v>
       </c>
-      <c r="AB33" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD33" t="s">
+      <c r="AB43" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="34" spans="4:30">
-      <c r="D34" t="s">
+    <row r="44" spans="4:28">
+      <c r="D44" t="s">
         <v>407</v>
       </c>
-      <c r="AB34" t="s">
-        <v>293</v>
-      </c>
-      <c r="AD34" t="s">
+      <c r="AB44" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="35" spans="4:30">
-      <c r="D35" t="s">
+    <row r="45" spans="4:28">
+      <c r="D45" t="s">
         <v>408</v>
       </c>
-      <c r="AB35" t="s">
-        <v>294</v>
-      </c>
-      <c r="AD35" t="s">
+      <c r="AB45" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="36" spans="4:30">
-      <c r="D36" t="s">
+    <row r="46" spans="4:28">
+      <c r="D46" t="s">
         <v>409</v>
       </c>
-      <c r="AB36" t="s">
-        <v>295</v>
-      </c>
-      <c r="AD36" t="s">
+      <c r="AB46" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="4:30">
-      <c r="D37" t="s">
+    <row r="47" spans="4:28">
+      <c r="D47" t="s">
         <v>410</v>
       </c>
-      <c r="AD37" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="38" spans="4:30">
-      <c r="D38" t="s">
+    </row>
+    <row r="48" spans="4:28">
+      <c r="D48" t="s">
         <v>411</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="39" spans="4:30">
-      <c r="D39" t="s">
-        <v>412</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="40" spans="4:30">
-      <c r="D40" t="s">
-        <v>413</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="41" spans="4:30">
-      <c r="D41" t="s">
-        <v>414</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="42" spans="4:30">
-      <c r="D42" t="s">
-        <v>415</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="43" spans="4:30">
-      <c r="D43" t="s">
-        <v>416</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="44" spans="4:30">
-      <c r="D44" t="s">
-        <v>417</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="45" spans="4:30">
-      <c r="D45" t="s">
-        <v>418</v>
-      </c>
-      <c r="AD45" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="46" spans="4:30">
-      <c r="D46" t="s">
-        <v>419</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="47" spans="4:30">
-      <c r="D47" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="48" spans="4:30">
-      <c r="D48" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="4:4">
       <c r="D52" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="85" spans="4:4">
       <c r="D85" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86" spans="4:4">
       <c r="D86" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -32466,7 +32620,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8F2B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9CBF" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -36556,7 +36710,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="901C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EEF6" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -40712,7 +40866,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A20C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BC66" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -40732,7 +40886,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1005"/>
+  <dimension ref="A1:M1005"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -40744,14 +40898,13 @@
     <col min="7" max="7" width="99.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="105.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="49.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="87.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="182.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="56.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="103.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="182.42578125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -40768,83 +40921,77 @@
         <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>96</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>78</v>
@@ -40853,37 +41000,34 @@
         <v>97</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
@@ -40899,75 +41043,74 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:13">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:13">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:13">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -46908,11 +47051,11 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="815C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="CD35" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:N4">
+  <conditionalFormatting sqref="A1:M4">
     <cfRule type="notContainsErrors" dxfId="0" priority="1">
       <formula>NOT(ISERROR(A1))</formula>
     </cfRule>
@@ -46928,7 +47071,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD1005"/>
+  <dimension ref="A1:AB1005"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -46948,298 +47091,278 @@
     <col min="15" max="15" width="131.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="97.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="67.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="120" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="86.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="198.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="162.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="106.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="72.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="60.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="53" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="61.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="64.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="66.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="61" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="79.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="47.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="46.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="53" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="64.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="66.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="61" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="79.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="47.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="46.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:28">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="L1" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="T1" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="V1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>256</v>
+      <c r="AA1" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="L2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="O2" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="U2" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>242</v>
-      </c>
       <c r="W2" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="Y2" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA2" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="Z2" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>257</v>
-      </c>
       <c r="AB2" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>217</v>
-      </c>
       <c r="L3" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="O3" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="R3" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>243</v>
-      </c>
       <c r="W3" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="Y3" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA3" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="Z3" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>258</v>
-      </c>
       <c r="AB3" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AD3" s="5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
@@ -47270,65 +47393,63 @@
       <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
       <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-    </row>
-    <row r="5" spans="1:30">
+    </row>
+    <row r="5" spans="1:28">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:28">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:28">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:28">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:28">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:28">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:28">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:28">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:28">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:28">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:28">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:28">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -52279,11 +52400,11 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F775" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="82DC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A4:AD4"/>
+    <mergeCell ref="A4:AB4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:AD4">
+  <conditionalFormatting sqref="A1:AB4">
     <cfRule type="notContainsErrors" dxfId="0" priority="1">
       <formula>NOT(ISERROR(A1))</formula>
     </cfRule>
@@ -52307,17 +52428,17 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="T5:T1005">
       <formula1>",Dual,Single"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="Z5:Z1005">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="X5:X1005">
       <formula1>",Cd41+,Cd41-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AB5:AB1005">
-      <formula1>HiddenDropdowns!$AB$5:$AB$36</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="Z5:Z1005">
+      <formula1>HiddenDropdowns!$Z$5:$Z$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AC5:AC1005">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AA5:AA1005">
       <formula1>",Genomic,Genomic Single Cell,Metagenomic,Metatranscriptomic,Other,Synthetic,Transcriptomic,Transcriptomic Single Cell,Viral Rna"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AD5:AD1005">
-      <formula1>HiddenDropdowns!$AD$5:$AD$46</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose from the list" sqref="AB5:AB1005">
+      <formula1>HiddenDropdowns!$AB$5:$AB$46</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52349,43 +52470,43 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -52393,43 +52514,43 @@
         <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>373</v>
-      </c>
       <c r="N2" s="5" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -52437,43 +52558,43 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="M3" s="5" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -56499,7 +56620,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AEAD" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FD65" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:N4"/>
   </mergeCells>
